--- a/data/trans_orig/IP07_C14_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C14_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling en su colegio en 2023 (tasa de respuesta: 94,11%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling en su colegio/instituto en 2023 (tasa de respuesta: 94,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7440</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12928</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9560</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7244</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>23956</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10921</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10921</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10921</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12661</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28438</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21441</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11128</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29915</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42274</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29944</t>
+          <t>31893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>167985</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159279</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>175056</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>132683</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>124209</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142996</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>169377</t>
+          <t>115391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159379</t>
+          <t>107837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176966</t>
+          <t>121748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>302060</t>
+          <t>283376</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289144</t>
+          <t>271488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314390</t>
+          <t>293028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187717</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187717</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187717</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>154124</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>154124</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>154124</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190210</t>
+          <t>137204</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>190210</t>
+          <t>137204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>190210</t>
+          <t>137204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>344334</t>
+          <t>324921</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>344334</t>
+          <t>324921</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>344334</t>
+          <t>324921</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1461</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7829</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36562</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31369</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40688</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33136</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29053</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35421</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68695</t>
+          <t>71361</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61884</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73669</t>
+          <t>76666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46142</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46142</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46142</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>36882</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36882</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36882</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>82427</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82427</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82427</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31593</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42528</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26548</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73927</t>
+          <t>72535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>217475</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>206540</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>175379</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>165392</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>185392</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217506</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204723</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>167437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>392885</t>
+          <t>378694</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378906</t>
+          <t>365042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>391316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
